--- a/output/pdf_financials_xlsx/DR.xlsx
+++ b/output/pdf_financials_xlsx/DR.xlsx
@@ -995,46 +995,46 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>26.169</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>14.582</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>6.709</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>4.742</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>3.538</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>3.024</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>4.258</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>5.892</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>3.488</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>7.903</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>5.731</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>5.637</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>3.191</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>1.322</v>
       </c>
     </row>
     <row r="13">
@@ -1870,46 +1870,46 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>22.074</v>
+        <v>-4.095</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>21.03</v>
+        <v>6.448</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>40.057</v>
+        <v>33.348</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>33.247</v>
+        <v>28.505</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>65.477</v>
+        <v>61.939</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>94.898</v>
+        <v>91.874</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>38.694</v>
+        <v>34.436</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>53.114</v>
+        <v>47.222</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>62.601</v>
+        <v>59.113</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>71.70699999999999</v>
+        <v>63.804</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>17.503</v>
+        <v>11.772</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>34.91</v>
+        <v>29.273</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>42.251</v>
+        <v>39.06</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>39.588</v>
+        <v>38.266</v>
       </c>
     </row>
     <row r="28">
@@ -1968,46 +1968,46 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>42.05</v>
+        <v>15.881</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>40.425</v>
+        <v>25.843</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>52.766</v>
+        <v>46.057</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>50.375</v>
+        <v>45.633</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>81.495</v>
+        <v>77.95699999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>110.358</v>
+        <v>107.334</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>52.07</v>
+        <v>47.812</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>69.348</v>
+        <v>63.456</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>76.46299999999999</v>
+        <v>72.97499999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>85.04300000000001</v>
+        <v>77.14</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>18.141</v>
+        <v>12.41</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>36.218</v>
+        <v>30.581</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>42.251</v>
+        <v>39.06</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>39.588</v>
+        <v>38.266</v>
       </c>
     </row>
     <row r="30">
@@ -43526,7 +43526,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -45878,7 +45878,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -46888,7 +46888,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -48578,7 +48578,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -50442,7 +50442,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -51218,7 +51218,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -52660,7 +52660,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E546" s="5" t="n">

--- a/output/pdf_financials_xlsx/DR.xlsx
+++ b/output/pdf_financials_xlsx/DR.xlsx
@@ -1922,43 +1922,43 @@
         <v>19.976</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>19.395</v>
+        <v>6.885</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>12.709</v>
+        <v>7.121</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>17.128</v>
+        <v>9.465</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>16.018</v>
+        <v>9.573</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.46</v>
+        <v>8.909000000000001</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>13.376</v>
+        <v>9.255000000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>16.234</v>
+        <v>11.512</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>13.862</v>
+        <v>10.404</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>13.336</v>
+        <v>19.872</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.638</v>
+        <v>20.125</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1.308</v>
+        <v>16.997</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>10.928</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="29">
@@ -1971,43 +1971,43 @@
         <v>15.881</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>25.843</v>
+        <v>13.333</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46.057</v>
+        <v>40.469</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>45.633</v>
+        <v>37.97</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>77.95699999999999</v>
+        <v>71.512</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>107.334</v>
+        <v>100.783</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>47.812</v>
+        <v>43.691</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>63.456</v>
+        <v>58.734</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>72.97499999999999</v>
+        <v>69.517</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>77.14</v>
+        <v>83.676</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>12.41</v>
+        <v>31.897</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>30.581</v>
+        <v>46.27</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>39.06</v>
+        <v>49.988</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>38.266</v>
+        <v>49.456</v>
       </c>
     </row>
     <row r="30">
@@ -5453,40 +5453,40 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>6.739</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>6.885</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>7.121</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>9.465</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>9.98</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>9.083</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>9.255000000000001</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>11.512</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>11.772</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>20.125</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>20.229</v>
       </c>
       <c r="N100" s="1" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.499</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -22776,7 +22776,11 @@
           <t>Depreciation of property and equipment 5</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -22848,7 +22852,11 @@
           <t>Depreciation of right-of-use assets 17.1</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -26270,7 +26278,11 @@
           <t>Depreciation of right-of-use assets 18.1</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -29302,7 +29314,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -30310,7 +30326,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -34280,7 +34300,11 @@
           <t>Depreciation of property and equipment 3</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -36306,7 +36330,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E349" s="5" t="n">
         <v>6.739</v>
       </c>
@@ -38566,7 +38594,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -42994,7 +43026,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -43072,7 +43108,11 @@
           <t>Depreciation of right-of-use assets 18.1</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -45560,7 +45600,11 @@
           <t>Depreciation of property and equipment 5</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -45632,7 +45676,11 @@
           <t>Depreciation of right-of-use assets 17.1</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -48152,7 +48200,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -50016,7 +50068,11 @@
           <t>Depreciation of property and equipment 3</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -51044,7 +51100,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E527" t="inlineStr">
         <is>
           <t>-</t>
